--- a/data/trans_orig/Q5408-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5408-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar el bater en 2007</t>
+          <t>Población según si es capaz de usar el bater en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,97 +733,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2080</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,62 +881,62 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>5422</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>950</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>4650</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55038</t>
+          <t>55061</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27881</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29709</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>84843</t>
+          <t>84071</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1189,97 +1189,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1870</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1868</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1904</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1302,97 +1302,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1870</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1868</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1904</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48960</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50830</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13918</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15786</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64712</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66616</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1645,97 +1645,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1762</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5993</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>24,69%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>5596</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>5663</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>23,05%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>1141</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>6371</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1698</t>
+          <t>1683</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9415</t>
+          <t>9579</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>4282</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>2554</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11226</t>
+          <t>11081</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62339</t>
+          <t>62175</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70056</t>
+          <t>70071</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17599</t>
+          <t>17721</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>83717</t>
+          <t>82659</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>93182</t>
+          <t>93130</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,98%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>3802</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,62 +2136,62 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>838</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1846</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>4185</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>838</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3397</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5520</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17389</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7484</t>
+          <t>7018</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6767</t>
+          <t>7047</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20243</t>
+          <t>19938</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>241662</t>
+          <t>241699</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>253832</t>
+          <t>254523</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>78268</t>
+          <t>78734</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>324807</t>
+          <t>324594</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>338384</t>
+          <t>338002</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4674</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>4913</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6537</t>
+          <t>6054</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4555</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18037</t>
+          <t>17812</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6414</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>20071</t>
+          <t>20628</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>48184</t>
+          <t>48138</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54632</t>
+          <t>54638</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>78213</t>
+          <t>78438</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91695</t>
+          <t>91117</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>130474</t>
+          <t>130114</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>144420</t>
+          <t>144562</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11518</t>
+          <t>11447</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11196</t>
+          <t>11781</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10184</t>
+          <t>10934</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28112</t>
+          <t>28846</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10349</t>
+          <t>10998</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28505</t>
+          <t>28788</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>392175</t>
+          <t>391333</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>411396</t>
+          <t>410747</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>395438</t>
+          <t>395493</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>414555</t>
+          <t>415320</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,88%</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5500</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2082</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12166</t>
+          <t>12641</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14585</t>
+          <t>15128</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10781</t>
+          <t>10542</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>25964</t>
+          <t>26024</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>21517</t>
+          <t>21485</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>45873</t>
+          <t>46508</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>35307</t>
+          <t>36486</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>64418</t>
+          <t>64924</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>473905</t>
+          <t>473585</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>489665</t>
+          <t>489762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>625105</t>
+          <t>624222</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>651198</t>
+          <t>650411</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1105762</t>
+          <t>1104344</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1135699</t>
+          <t>1134704</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar el bater en 2012</t>
+          <t>Población según si es capaz de usar el bater en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4159,97 +4159,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2151</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2091</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2171</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>6343</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5978</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7316</t>
+          <t>7064</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39353</t>
+          <t>37575</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19311</t>
+          <t>20488</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>61891</t>
+          <t>62143</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -4615,97 +4615,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1113</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2230</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4796</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>25,37%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>1113</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>4620</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>5,89%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>5257</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>24,44%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1113</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4680</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7194</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5748</t>
+          <t>4683</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8795</t>
+          <t>9558</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53436</t>
+          <t>52974</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12226</t>
+          <t>12624</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69152</t>
+          <t>68346</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78391</t>
+          <t>78428</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6176</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,62 +5106,62 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1971</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>5899</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>992</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>5053</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>947</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>8189</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>940</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8229</t>
+          <t>7290</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108413</t>
+          <t>109117</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>117589</t>
+          <t>117571</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>52644</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54615</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>163769</t>
+          <t>163435</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>172278</t>
+          <t>172274</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17036</t>
+          <t>16171</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>3021</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16442</t>
+          <t>17132</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>7714</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24354</t>
+          <t>24445</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>923</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>8153</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10415</t>
+          <t>10373</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28777</t>
+          <t>28233</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>197505</t>
+          <t>198512</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>218231</t>
+          <t>217924</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>51567</t>
+          <t>51942</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>59160</t>
+          <t>59172</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>254379</t>
+          <t>253985</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>275255</t>
+          <t>276026</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,58%</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7029</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3248</t>
+          <t>3256</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14639</t>
+          <t>15168</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18133</t>
+          <t>17743</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11582</t>
+          <t>10820</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>30538</t>
+          <t>29527</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>16021</t>
+          <t>16716</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>36375</t>
+          <t>36493</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>88213</t>
+          <t>89083</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>99617</t>
+          <t>99615</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>149788</t>
+          <t>149400</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>169485</t>
+          <t>169591</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>243043</t>
+          <t>244199</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>267068</t>
+          <t>265834</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,32%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5192</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20160</t>
+          <t>20177</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4460</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19075</t>
+          <t>19681</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13020</t>
+          <t>12901</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31757</t>
+          <t>31374</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13009</t>
+          <t>13125</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>31641</t>
+          <t>31246</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>350137</t>
+          <t>351217</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>373224</t>
+          <t>374239</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>352968</t>
+          <t>352956</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>375325</t>
+          <t>376228</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,84%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5088</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>20054</t>
+          <t>19167</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12017</t>
+          <t>11621</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>30898</t>
+          <t>30810</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>19967</t>
+          <t>20030</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>45394</t>
+          <t>42952</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>17673</t>
+          <t>16981</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>38257</t>
+          <t>38182</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>34376</t>
+          <t>34455</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>61243</t>
+          <t>61617</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>56608</t>
+          <t>56753</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>90980</t>
+          <t>91959</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>509032</t>
+          <t>509512</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>533280</t>
+          <t>533224</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>659302</t>
+          <t>659112</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>690990</t>
+          <t>691583</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1177973</t>
+          <t>1175288</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1217628</t>
+          <t>1217556</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,54%</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar el bater en 2016</t>
+          <t>Población según si es capaz de usar el bater en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7585,97 +7585,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1933</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2085</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6945</t>
+          <t>8754</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64196</t>
+          <t>63165</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29809</t>
+          <t>29458</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>98590</t>
+          <t>96781</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -8041,97 +8041,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2217</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>12,61%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1940</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>976</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8663</t>
+          <t>8889</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6383</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1712</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11508</t>
+          <t>11616</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,38%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44681</t>
+          <t>44455</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52375</t>
+          <t>52368</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11205</t>
+          <t>11632</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59424</t>
+          <t>59316</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69220</t>
+          <t>69012</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,62 +8532,62 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>892</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2322</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>5397</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>892</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>4557</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>781</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8437</t>
+          <t>8266</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6349</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8665,7 +8665,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10039</t>
+          <t>10419</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>111272</t>
+          <t>110421</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>119049</t>
+          <t>119351</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>39860</t>
+          <t>41255</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>155618</t>
+          <t>154326</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>164832</t>
+          <t>164523</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -8958,7 +8958,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6774</t>
+          <t>6674</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2232</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>810</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>6775</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4912</t>
+          <t>4839</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15929</t>
+          <t>15618</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11540</t>
+          <t>11592</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>8364</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22228</t>
+          <t>23286</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>185202</t>
+          <t>185500</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>197317</t>
+          <t>197257</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>87506</t>
+          <t>87454</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>97730</t>
+          <t>97721</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>277273</t>
+          <t>277185</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>292768</t>
+          <t>292613</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7784</t>
+          <t>8186</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>6706</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>816</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10646</t>
+          <t>9416</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12812</t>
+          <t>13014</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>3879</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16786</t>
+          <t>16855</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>8405</t>
+          <t>9058</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>24763</t>
+          <t>26147</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>130290</t>
+          <t>128896</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>140861</t>
+          <t>140794</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>140327</t>
+          <t>140087</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>154425</t>
+          <t>154410</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>275319</t>
+          <t>274633</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>293237</t>
+          <t>292589</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,0%</t>
         </is>
       </c>
     </row>
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22104</t>
+          <t>21948</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22104</t>
+          <t>21948</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9088</t>
+          <t>9862</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26629</t>
+          <t>29808</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9088</t>
+          <t>9862</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>26629</t>
+          <t>29808</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>371386</t>
+          <t>368119</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>394159</t>
+          <t>393826</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>371386</t>
+          <t>368119</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>394159</t>
+          <t>393826</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2419</t>
+          <t>2427</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11749</t>
+          <t>11545</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6476</t>
+          <t>6843</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>24104</t>
+          <t>23048</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11753</t>
+          <t>11090</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>31538</t>
+          <t>29164</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>16112</t>
+          <t>15626</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>34329</t>
+          <t>34446</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>23448</t>
+          <t>23167</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>49137</t>
+          <t>48516</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>45433</t>
+          <t>44029</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>74767</t>
+          <t>74722</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>550747</t>
+          <t>550407</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>571065</t>
+          <t>570953</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>707619</t>
+          <t>707979</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>736658</t>
+          <t>736552</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1267360</t>
+          <t>1268608</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1302334</t>
+          <t>1303013</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,55%</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10816,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar el bater en 2023</t>
+          <t>Población según si es capaz de usar el bater en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11011,97 +11011,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>942</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1092</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11129,7 +11129,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2766</t>
+          <t>2802</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11164,7 +11164,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3431</t>
+          <t>3314</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>336</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3819</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -11237,7 +11237,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>104813</t>
+          <t>104777</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -11252,7 +11252,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61890</t>
+          <t>62007</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>169081</t>
+          <t>168799</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>172569</t>
+          <t>172564</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,7 +11322,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -11467,12 +11467,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>396</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>4125</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>386</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -11585,7 +11585,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11600,7 +11600,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11620,7 +11620,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>3793</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91908</t>
+          <t>91928</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -11708,7 +11708,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42181</t>
+          <t>42184</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46383</t>
+          <t>46346</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>136130</t>
+          <t>136036</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>140994</t>
+          <t>140974</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4513</t>
+          <t>4657</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>355</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4453</t>
+          <t>3928</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12013,7 +12013,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9257</t>
+          <t>9021</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>607</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3354</t>
+          <t>3177</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11388</t>
+          <t>10836</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>91516</t>
+          <t>91034</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>99028</t>
+          <t>98891</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48460</t>
+          <t>47910</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>52191</t>
+          <t>52182</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>141401</t>
+          <t>142322</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>150466</t>
+          <t>150653</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>343</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7426</t>
+          <t>7059</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12419,7 +12419,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4637</t>
+          <t>4399</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12434,7 +12434,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>506</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8663</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12469,7 +12469,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15371</t>
+          <t>15590</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>976</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16656</t>
+          <t>16812</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27731</t>
+          <t>26270</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>219875</t>
+          <t>219675</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>230501</t>
+          <t>230885</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>307016</t>
+          <t>306532</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>325565</t>
+          <t>325482</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>531851</t>
+          <t>532935</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>558551</t>
+          <t>559767</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -12840,7 +12840,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>2706</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9714</t>
+          <t>9243</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10657</t>
+          <t>11060</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1624</t>
+          <t>1707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7728</t>
+          <t>7896</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12264</t>
+          <t>12343</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23486</t>
+          <t>23085</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14951</t>
+          <t>15821</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>27801</t>
+          <t>27461</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>83340</t>
+          <t>83438</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89747</t>
+          <t>89774</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>175605</t>
+          <t>175651</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>187885</t>
+          <t>188085</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>262531</t>
+          <t>262779</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>276628</t>
+          <t>276007</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,89%</t>
         </is>
       </c>
     </row>
@@ -13291,12 +13291,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4417</t>
+          <t>4740</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12721</t>
+          <t>12687</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4428</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>13242</t>
+          <t>13151</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -13404,12 +13404,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>23297</t>
+          <t>22520</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39213</t>
+          <t>38325</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>22026</t>
+          <t>23307</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>39241</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -13517,12 +13517,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2358</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>273639</t>
+          <t>273609</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>291420</t>
+          <t>291702</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>277797</t>
+          <t>276579</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>295839</t>
+          <t>294482</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,64%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9043</t>
+          <t>9761</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8047</t>
+          <t>8195</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>24497</t>
+          <t>23475</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,47 +13797,47 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>20668</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>13010</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>28995</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>0,79%</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>20668</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>12892</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>29094</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13755</t>
+          <t>13775</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>27063</t>
+          <t>27416</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>27933</t>
+          <t>28415</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>73650</t>
+          <t>73868</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>49059</t>
+          <t>48663</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>91572</t>
+          <t>92009</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>605791</t>
+          <t>605903</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>620460</t>
+          <t>620878</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>924888</t>
+          <t>924360</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>984788</t>
+          <t>980302</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1540906</t>
+          <t>1541902</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1594931</t>
+          <t>1593069</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,17%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5408-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5408-Clase-trans_orig.xlsx
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4765</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5422</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55061</t>
+          <t>55019</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>84071</t>
+          <t>84079</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>5430</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>6319</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1683</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9579</t>
+          <t>9965</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4282</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2554</t>
+          <t>2545</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11081</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,76%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62175</t>
+          <t>61789</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70071</t>
+          <t>70042</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17721</t>
+          <t>16824</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>82659</t>
+          <t>82866</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>93130</t>
+          <t>93150</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3802</t>
+          <t>4198</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>4226</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>5476</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17516</t>
+          <t>16856</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7018</t>
+          <t>6684</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7047</t>
+          <t>7201</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19938</t>
+          <t>21037</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>241699</t>
+          <t>241845</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>254523</t>
+          <t>254437</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>78734</t>
+          <t>79068</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>324594</t>
+          <t>323945</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>338002</t>
+          <t>338382</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>4611</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4913</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6054</t>
+          <t>6032</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17812</t>
+          <t>18043</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>20628</t>
+          <t>20240</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>48138</t>
+          <t>48451</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54638</t>
+          <t>54626</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>78438</t>
+          <t>78207</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91117</t>
+          <t>90928</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>130114</t>
+          <t>130517</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>144562</t>
+          <t>145155</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11447</t>
+          <t>11455</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11781</t>
+          <t>10382</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10934</t>
+          <t>11164</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28846</t>
+          <t>28485</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10998</t>
+          <t>11178</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28788</t>
+          <t>29195</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>391333</t>
+          <t>391679</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>410747</t>
+          <t>410784</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>395493</t>
+          <t>395289</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>415320</t>
+          <t>414310</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>5892</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12641</t>
+          <t>12102</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>15128</t>
+          <t>16341</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10542</t>
+          <t>10913</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26024</t>
+          <t>26490</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>21485</t>
+          <t>22058</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>46508</t>
+          <t>44987</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>36486</t>
+          <t>36042</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>64924</t>
+          <t>63625</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>473585</t>
+          <t>473412</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>489762</t>
+          <t>489318</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>624222</t>
+          <t>625202</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>650411</t>
+          <t>649307</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1104344</t>
+          <t>1106621</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1134704</t>
+          <t>1136533</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6343</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7064</t>
+          <t>7494</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37575</t>
+          <t>38563</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20488</t>
+          <t>19759</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>62143</t>
+          <t>61713</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>5812</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5257</t>
+          <t>6325</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7656</t>
+          <t>7220</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4683</t>
+          <t>5389</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9558</t>
+          <t>9076</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52974</t>
+          <t>53410</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12624</t>
+          <t>12078</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68346</t>
+          <t>69920</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78428</t>
+          <t>78420</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5899</t>
+          <t>5018</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>8181</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>953</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7290</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>109117</t>
+          <t>108554</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>117571</t>
+          <t>117619</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>163435</t>
+          <t>163892</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>172274</t>
+          <t>172251</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>3125</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17132</t>
+          <t>17124</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7714</t>
+          <t>8291</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24445</t>
+          <t>24537</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>924</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8153</t>
+          <t>8533</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10373</t>
+          <t>10548</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28233</t>
+          <t>27030</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>198512</t>
+          <t>198310</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>217924</t>
+          <t>217988</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>51942</t>
+          <t>51562</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>59172</t>
+          <t>59171</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>253985</t>
+          <t>256623</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>276026</t>
+          <t>276058</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,59%</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3256</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15168</t>
+          <t>15502</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5201</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17743</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10820</t>
+          <t>10626</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>12176</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29527</t>
+          <t>29731</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>16716</t>
+          <t>17077</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>36493</t>
+          <t>36914</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>89083</t>
+          <t>89010</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>99615</t>
+          <t>99639</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>149400</t>
+          <t>149096</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>169591</t>
+          <t>169495</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>244199</t>
+          <t>242641</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>265834</t>
+          <t>266555</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,57%</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>5094</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20177</t>
+          <t>18970</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,47 +6489,47 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>10518</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>5190</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>19792</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
           <t>1,31%</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>5,11%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>10518</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>5068</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>19681</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12901</t>
+          <t>12678</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31374</t>
+          <t>30898</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13125</t>
+          <t>13148</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>31246</t>
+          <t>31938</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>351217</t>
+          <t>350730</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>374239</t>
+          <t>373446</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>352956</t>
+          <t>353598</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>376228</t>
+          <t>375084</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,55%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>19167</t>
+          <t>19239</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>11621</t>
+          <t>11819</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>30810</t>
+          <t>30509</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>20030</t>
+          <t>19595</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>42952</t>
+          <t>43356</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>16981</t>
+          <t>17218</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>38182</t>
+          <t>38520</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>34455</t>
+          <t>32699</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>61617</t>
+          <t>59748</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>56753</t>
+          <t>57160</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>91959</t>
+          <t>91243</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>509512</t>
+          <t>509255</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>533224</t>
+          <t>532930</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>659112</t>
+          <t>659895</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>691583</t>
+          <t>692046</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1175288</t>
+          <t>1177638</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1217556</t>
+          <t>1217438</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>6476</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8754</t>
+          <t>8751</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>63165</t>
+          <t>64412</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29458</t>
+          <t>30412</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>96781</t>
+          <t>96784</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8889</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5956</t>
+          <t>5970</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11616</t>
+          <t>11577</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44455</t>
+          <t>44680</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52368</t>
+          <t>52312</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11632</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59316</t>
+          <t>59355</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69012</t>
+          <t>68994</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,27%</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4520</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>5395</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>795</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8266</t>
+          <t>8264</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8665,7 +8665,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>1192</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10419</t>
+          <t>9703</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>110421</t>
+          <t>110735</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>119351</t>
+          <t>119049</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>41255</t>
+          <t>40650</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>154326</t>
+          <t>155493</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>164523</t>
+          <t>164810</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>811</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6674</t>
+          <t>6762</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>798</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6775</t>
+          <t>6646</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>4351</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15618</t>
+          <t>16203</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11592</t>
+          <t>11191</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>8326</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23286</t>
+          <t>22778</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>185500</t>
+          <t>184693</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>197257</t>
+          <t>197279</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>87454</t>
+          <t>87855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>97721</t>
+          <t>97756</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>277185</t>
+          <t>277148</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>292613</t>
+          <t>292756</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8186</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6706</t>
+          <t>6785</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>807</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>9791</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13014</t>
+          <t>12880</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3879</t>
+          <t>3783</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16855</t>
+          <t>16468</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>9058</t>
+          <t>8615</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>26147</t>
+          <t>25509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>128896</t>
+          <t>129653</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>140794</t>
+          <t>140335</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>140087</t>
+          <t>141393</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>154410</t>
+          <t>155597</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>274633</t>
+          <t>275016</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>292589</t>
+          <t>293503</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5681</t>
+          <t>5093</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>21948</t>
+          <t>21573</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5681</t>
+          <t>5093</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>21948</t>
+          <t>21573</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9862</t>
+          <t>9391</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29808</t>
+          <t>27611</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9862</t>
+          <t>9391</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>29808</t>
+          <t>27611</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>368119</t>
+          <t>370629</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>393826</t>
+          <t>394285</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>368119</t>
+          <t>370629</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>393826</t>
+          <t>394285</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,45%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2427</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11545</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6843</t>
+          <t>6521</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>23048</t>
+          <t>24478</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11090</t>
+          <t>11113</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>29164</t>
+          <t>30202</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>15626</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>34446</t>
+          <t>34177</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>23167</t>
+          <t>24026</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>48516</t>
+          <t>49280</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>44029</t>
+          <t>44202</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>74722</t>
+          <t>75350</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>550407</t>
+          <t>551194</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>570953</t>
+          <t>571412</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>707979</t>
+          <t>707969</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>736552</t>
+          <t>738078</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10602,7 +10602,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1268608</t>
+          <t>1266467</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1303013</t>
+          <t>1302964</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,7 +10632,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -11119,7 +11119,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>835</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -11129,12 +11129,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11154,7 +11154,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>615</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -11164,12 +11164,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11189,32 +11189,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>312</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>4093</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -11232,27 +11232,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>106733</t>
+          <t>119566</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>104777</t>
+          <t>117450</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -11267,27 +11267,27 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>64771</t>
+          <t>73944</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62007</t>
+          <t>71587</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -11302,32 +11302,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>171503</t>
+          <t>193509</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>168799</t>
+          <t>190867</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>172564</t>
+          <t>194648</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -11345,17 +11345,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11380,17 +11380,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11415,17 +11415,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11497,32 +11497,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>393</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4125</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11532,32 +11532,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>397</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -11575,7 +11575,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>598</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -11585,92 +11585,92 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2910</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>5,25%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>1029</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>3400</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
           <t>0,64%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>411</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>2098</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>4,47%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1023</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>3793</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -11688,27 +11688,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>94386</t>
+          <t>104117</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91928</t>
+          <t>101139</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>44987</t>
+          <t>53317</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42184</t>
+          <t>50558</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46346</t>
+          <t>54941</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>139373</t>
+          <t>157435</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>136036</t>
+          <t>154049</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>140974</t>
+          <t>159248</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -11801,17 +11801,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11836,17 +11836,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11871,17 +11871,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11918,32 +11918,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>1469</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>342</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4657</t>
+          <t>4727</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11988,32 +11988,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>1469</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>342</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3928</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -12031,32 +12031,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4494</t>
+          <t>4609</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9021</t>
+          <t>9543</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1673</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>578</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>5338</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>6556</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3177</t>
+          <t>3307</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10836</t>
+          <t>11480</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -12144,32 +12144,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>96115</t>
+          <t>106392</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>91034</t>
+          <t>101236</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>98891</t>
+          <t>109278</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12179,32 +12179,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>51116</t>
+          <t>56023</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47910</t>
+          <t>52632</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>52182</t>
+          <t>57392</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>147230</t>
+          <t>162416</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>142322</t>
+          <t>157147</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>150653</t>
+          <t>165966</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -12257,17 +12257,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12292,17 +12292,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12374,32 +12374,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2257</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>340</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7059</t>
+          <t>6922</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12409,32 +12409,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>312</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4399</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12444,32 +12444,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3473</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>8330</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -12487,32 +12487,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9877</t>
+          <t>10422</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15590</t>
+          <t>16342</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12522,32 +12522,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5592</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>2842</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16812</t>
+          <t>9932</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12557,32 +12557,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>15183</t>
+          <t>16014</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>11057</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26270</t>
+          <t>22568</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -12600,32 +12600,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>226063</t>
+          <t>247261</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>219675</t>
+          <t>240567</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>230885</t>
+          <t>252502</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12635,32 +12635,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>320242</t>
+          <t>124138</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>306532</t>
+          <t>119614</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>325482</t>
+          <t>127243</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12670,32 +12670,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>546305</t>
+          <t>371398</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>532935</t>
+          <t>363768</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>559767</t>
+          <t>377175</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>96,49%</t>
         </is>
       </c>
     </row>
@@ -12713,17 +12713,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>238197</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>238197</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>238197</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12748,17 +12748,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12783,17 +12783,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>564890</t>
+          <t>390886</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>564890</t>
+          <t>390886</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>564890</t>
+          <t>390886</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12830,7 +12830,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>831</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -12840,12 +12840,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2668</t>
+          <t>3438</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12865,32 +12865,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5474</t>
+          <t>5894</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9243</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12900,32 +12900,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>6725</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11060</t>
+          <t>12254</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -12943,32 +12943,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1707</t>
+          <t>1690</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7896</t>
+          <t>7975</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12978,32 +12978,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>17180</t>
+          <t>17699</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12343</t>
+          <t>12829</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23085</t>
+          <t>23693</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13013,32 +13013,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>20930</t>
+          <t>21549</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>15821</t>
+          <t>16379</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>27461</t>
+          <t>29471</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -13056,32 +13056,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>87434</t>
+          <t>96112</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>83438</t>
+          <t>91610</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89774</t>
+          <t>98467</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13091,32 +13091,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>182479</t>
+          <t>196651</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>175651</t>
+          <t>189725</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>188085</t>
+          <t>202161</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13126,32 +13126,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>269913</t>
+          <t>292763</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>262779</t>
+          <t>284672</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>276007</t>
+          <t>299062</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>93,16%</t>
         </is>
       </c>
     </row>
@@ -13169,17 +13169,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13204,17 +13204,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13239,17 +13239,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>297139</t>
+          <t>321037</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>297139</t>
+          <t>321037</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>297139</t>
+          <t>321037</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -13321,32 +13321,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7976</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4740</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12687</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13356,32 +13356,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>7976</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4362</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>13151</t>
+          <t>15124</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -13434,32 +13434,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>30056</t>
+          <t>32211</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22520</t>
+          <t>24463</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38325</t>
+          <t>41599</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13469,32 +13469,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>30056</t>
+          <t>32211</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>23307</t>
+          <t>24008</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>39241</t>
+          <t>41405</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -13512,7 +13512,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -13547,32 +13547,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>283640</t>
+          <t>304545</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>273609</t>
+          <t>293087</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>291702</t>
+          <t>312430</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13582,32 +13582,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>286844</t>
+          <t>307821</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>276579</t>
+          <t>298250</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>294482</t>
+          <t>317193</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,87%</t>
         </is>
       </c>
     </row>
@@ -13625,17 +13625,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13660,17 +13660,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13695,17 +13695,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13742,32 +13742,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>4538</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9761</t>
+          <t>9429</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13777,32 +13777,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>16130</t>
+          <t>17707</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8195</t>
+          <t>12338</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>23475</t>
+          <t>25054</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13812,32 +13812,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>20668</t>
+          <t>22330</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>13010</t>
+          <t>15596</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>28995</t>
+          <t>30389</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -13855,32 +13855,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>19580</t>
+          <t>20315</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13775</t>
+          <t>13952</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>27416</t>
+          <t>28555</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13890,32 +13890,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>55176</t>
+          <t>58496</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>28415</t>
+          <t>48340</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>73868</t>
+          <t>70571</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13925,32 +13925,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>74756</t>
+          <t>78811</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>48663</t>
+          <t>66965</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>92009</t>
+          <t>93230</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -13968,32 +13968,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>613935</t>
+          <t>676725</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>605903</t>
+          <t>668255</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>620878</t>
+          <t>683837</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14003,32 +14003,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>947233</t>
+          <t>808618</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>924360</t>
+          <t>795444</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>980302</t>
+          <t>820811</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14038,32 +14038,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1561168</t>
+          <t>1485343</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1541902</t>
+          <t>1469209</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1593069</t>
+          <t>1498492</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>94,45%</t>
         </is>
       </c>
     </row>
@@ -14081,17 +14081,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>638053</t>
+          <t>701663</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>638053</t>
+          <t>701663</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>638053</t>
+          <t>701663</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14116,17 +14116,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1018539</t>
+          <t>884821</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1018539</t>
+          <t>884821</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1018539</t>
+          <t>884821</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14151,17 +14151,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1656592</t>
+          <t>1586484</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1656592</t>
+          <t>1586484</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1656592</t>
+          <t>1586484</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
